--- a/quizzes/004_sourdough_knowledge_assessment--quizzes.xlsx
+++ b/quizzes/004_sourdough_knowledge_assessment--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>learning_needs</t>
+          <t>learning_needs_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What do you want to learn about sourdough?</t>
+          <t>Learning Needs 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission status</t>
+          <t>Submission Status 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>baking_time</t>
+          <t>baking_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baking time</t>
+          <t>Baking Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sourdough_kneading_time</t>
+          <t>sourdough_kneading_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sourdough kneading time</t>
+          <t>Sourdough Kneading Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sourdough_bread_shape</t>
+          <t>sourdough_bread_shape_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sourdough bread shape</t>
+          <t>Sourdough Bread Shape 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>baking_environment</t>
+          <t>baking_environment_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baking environment</t>
+          <t>Baking Environment 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sourdough_bread_temperature</t>
+          <t>sourdough_bread_temperature_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sourdough bread temperature</t>
+          <t>Sourdough Bread Temperature 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>learning_needs</t>
+          <t>learning_needs_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What do you want to learn about sourdough?</t>
+          <t>Learning Needs 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submission status</t>
+          <t>Submission Status 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submission status 2</t>
+          <t>Submission Status2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,318 +1420,318 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sourdough_bread_shape_choices</t>
+          <t>sourdough_bread_shape_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sourdough_bread_shape_choices</t>
+          <t>sourdough_bread_shape_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sourdough_bread_shape_choices</t>
+          <t>sourdough_bread_shape_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>baking_environment_choices</t>
+          <t>baking_environment_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baking_environment_choices</t>
+          <t>baking_environment_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baking_environment_choices</t>
+          <t>baking_environment_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sourdough_bread_temperature_choices</t>
+          <t>sourdough_bread_temperature_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sourdough_bread_temperature_choices</t>
+          <t>sourdough_bread_temperature_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sourdough_bread_temperature_choices</t>
+          <t>sourdough_bread_temperature_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>learning_needs_choices</t>
+          <t>learning_needs_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
